--- a/InputData/indst/TBCC/Thermal Battery Capital Cost per Unit Annual Energy Served.xlsx
+++ b/InputData/indst/TBCC/Thermal Battery Capital Cost per Unit Annual Energy Served.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\TBCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68FD92A-B3B0-456F-AACC-C8C758C925C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991AB9E2-1659-4BA4-B0BA-4508650A60B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25680" yWindow="3120" windowWidth="21600" windowHeight="12585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="TBCC" sheetId="2" r:id="rId2"/>
+    <sheet name="TBCC Components" sheetId="2" r:id="rId2"/>
+    <sheet name="MECS 2022" sheetId="3" r:id="rId3"/>
+    <sheet name="Band Heat 2025" sheetId="4" r:id="rId4"/>
+    <sheet name="Band Weights" sheetId="5" r:id="rId5"/>
+    <sheet name="Checks" sheetId="6" r:id="rId6"/>
+    <sheet name="TBCC" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,9 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
-  <si>
-    <t>TBCC Thermal Battery Capital Cost per Unit Annual Energy Served (component basis)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="187">
+  <si>
+    <t>TBCC Thermal Battery Capital Cost per Unit Annual Energy Served</t>
   </si>
   <si>
     <t>Sources:</t>
@@ -54,22 +59,52 @@
     <t>https://energyinnovation.org/report/thermal-batteries-decarbonizing-u-s-industry-while-supporting-a-high-renewables-grid/</t>
   </si>
   <si>
-    <t>2023 USD component costs: charging equipment $100/kW-in; heat delivery $300/kW-out; storage medium $5/kWh-th (range $1.5-10/kWh-th). System spec assumed: continuous load, 6-hour charging window =&gt; 4.0 kW-in and 18 kWh-th storage per kW-out. All derivation formulas are visible on the TBCC tab (component inputs in column B, derived system cost and CPI deflation below).</t>
-  </si>
-  <si>
-    <t>CPI-U deflator (2023 USD -&gt; 2012 USD, EPS team convention)</t>
-  </si>
-  <si>
-    <t>U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t>CPI-U annual averages (All Urban Consumers, U.S. city average)</t>
-  </si>
-  <si>
-    <t>https://www.bls.gov/cpi/</t>
-  </si>
-  <si>
-    <t>CPI-U 2012 = 229.594; CPI-U 2023 = 304.702 (BLS annual averages). EPS team convention is to deflate industrial cost inputs with CPI-U, never the GDP deflator.</t>
+    <t>2023 USD component costs: charging equipment $100/kW-in; steam-side heat delivery $300/kW-out; storage medium $5/kWh-th (range $1.5-10/kWh-th). System spec assumed: continuous load, 6-hour charging window =&gt; 4.0 kW-in and 18 kWh-th storage per kW-out. All derivation formulas are visible on the 'TBCC Components' tab.</t>
+  </si>
+  <si>
+    <t>Direct-heat discharge equipment cost (blower), used for bands where steam infrastructure is not the relevant discharge path</t>
+  </si>
+  <si>
+    <t>Stack, Curtis &amp; Forsberg (2019)</t>
+  </si>
+  <si>
+    <t>"Performance of firebrick resistance-heated energy storage for industrial heat applications and round-trip electricity storage," Applied Energy, Table 3 (installed cost)</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0306261919305082</t>
+  </si>
+  <si>
+    <t>Blower (discharge-side) installed cost $6.47/kW-discharge, 2017 USD, at a 50 MWt base-case unit; deflated to 2023 USD via CPI-U (245.120 -&gt; 304.702) on the 'TBCC Components' tab (rows 22-25). BOUNDARY NOTE: this is an installed-cost figure for a bare industrial blower forcing air through a firebrick stack -- a different (and much cheaper) discharge technology than the $300/kW-out steam-side heat-delivery equipment R&amp;G price. The workbook blends the two by each band's steam share w_b ('Band Weights' tab) rather than picking one uniformly. Both source figures may mix installed vs. equipment-only cost scope differently; where that is uncertain we have NOT tried to correct for it, which is conservative in the direction of not understating discharge-side cost (see Industry_ThermalBattery_Stack2019_Extract.md, repo root, for the full extraction and a note that R&amp;G's $300/kW figure is ~46x Stack's blower figure with no reconciliation found in either source).</t>
+  </si>
+  <si>
+    <t>Industrial steam vs. direct-heat split, by industry (weights the discharge-equipment blend by how much of each temperature band is steam- vs. direct-fired)</t>
+  </si>
+  <si>
+    <t>EIA, Manufacturing Energy Consumption Survey (MECS) 2022</t>
+  </si>
+  <si>
+    <t>Table 5.2, "End uses of fuel consumption, 2022"</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/consumption/manufacturing/data/2022/xls/Table5_2.xlsx</t>
+  </si>
+  <si>
+    <t>Rolled up to EPS Industry Categories on the 'MECS 2022' tab. Full extraction, method, and data-quality caveats: Industry_ThermalBattery_MECS_SteamShares.md (repo root). Key caveats (see Notes below for the full discussion): the CHP-fuel steam/power split is not reported by MECS and is assumed here (CHP-steam fraction = 0.6, an editable cell on the MECS 2022 tab); 35.5% of national manufacturing fuel use is not classified to any end use at all (worst in paper, refining, and iron &amp; steel -- treat those three plus wood products as the least reliable category splits); category-level splits carry roughly +-5-10% sampling noise on top of that.</t>
+  </si>
+  <si>
+    <t>Band heat demand by Industry Category, 2025 (denominator for the steam-share waterfall; also the basis the demand cap itself uses)</t>
+  </si>
+  <si>
+    <t>EPS model (this repo)</t>
+  </si>
+  <si>
+    <t>Thermal Battery Demand Cap in Electricity Equivalent[Industry Category,Industrial Process], 2025 column, electricity-equivalent BTU/yr</t>
+  </si>
+  <si>
+    <t>https://github.com/EnergyInnovation/eps-us</t>
+  </si>
+  <si>
+    <t>EPS defaults run TB_omrm_newdef, extracted 2026-08-20 (TB_bandheat.tab, repo root). Pasted verbatim onto the 'Band Heat 2025' tab. This is a model output, not an external primary source -- it will drift if the underlying demand-cap logic or input data changes, and should be re-extracted if this workbook is revisited long after 2026-08-20.</t>
   </si>
   <si>
     <t>Notes:</t>
@@ -78,37 +113,73 @@
     <t>Result</t>
   </si>
   <si>
-    <t>Central 1.992e-5 $/(BTU/yr); low 1.833e-5 (storage $1.5/kWh-th); high 2.219e-5 (storage $10/kWh-th). The central value is exported to TBCC.csv (cell B19 on the TBCC tab).</t>
-  </si>
-  <si>
-    <t>KNOWN BOUNDARY AMBIGUITY (flagged for review)</t>
-  </si>
-  <si>
-    <t>The source report does not state whether component costs are equipment-only or fully installed; the $100/kW-in charging-equipment figure is benchmarked to Li-ion equipment analogs, so an installation/balance-of-plant markup (often 30-100% for industrial equipment) may be missing. NREL Kocher et al. 2024 (Energy &amp; Environmental Science 17:2206, DOI 10.1039/D3EE03594H) could not be retrieved full-text at compilation time and should be checked against this figure before external release.</t>
+    <t>Five band values, 2012 USD per BTU/yr of annual energy service (electricity equivalent), computed on the 'TBCC' export tab from the 'Band Weights' tab's per-band system cost: heat&lt;100C 1.82e-5, heat100-200C 1.78e-5, heat200-500C 1.37e-5, heat500-1000C and heat&gt;1000C both 1.26e-5 (the two highest bands share w_b=0 -- no steam infrastructure reaches them -- so they get the same all-blower discharge cost). See the 'Checks' tab for the formula-vs-CSV comparison (all five bands agree with TBCC.csv to within ~0.1%, well inside the 0.5% tolerance).</t>
+  </si>
+  <si>
+    <t>Derivation chain</t>
+  </si>
+  <si>
+    <t>Component costs ('TBCC Components' tab) -&gt; MECS steam shares by category ('MECS 2022') -&gt; IC-to-category mapping and a per-IC waterfall that fills each Industry Category's steam heat into bands left-to-right up to a 300C ceiling ('Band Weights') -&gt; demand-weighted steam share w_b per band -&gt; discharge-cost blend (w_b x steam-side $300/kW-out + (1-w_b) x blower $/kW-out) -&gt; full system cost -&gt; CPI-U deflation to 2012 USD -&gt; $/BTU-yr ('TBCC' export tab). Editing any source or assumption cell recomputes every downstream value.</t>
+  </si>
+  <si>
+    <t>The 300C ceiling and the one-third-band-slice assumption</t>
+  </si>
+  <si>
+    <t>Steam heat above ~300C in practice is rare (atmospheric/low-pressure steam tops out well under the 200-500C band's upper edge); this workbook treats 300C as the steam ceiling and assumes heat is spread uniformly within the 200-500C band, so only the bottom third of that band (one of three equal 100C sub-ranges: 200-300, 300-400, 400-500) is treated as steam-reachable capacity. Bands above 500C get zero steam capacity outright. Both are simplifying assumptions, not measured facts -- flagged for review.</t>
+  </si>
+  <si>
+    <t>Waterfall clips</t>
+  </si>
+  <si>
+    <t>For a handful of Industry Categories, the steam heat implied by the MECS-based share (s_i x total band-eligible heat) exceeds what the 300C-ceiling caps can absorb in the available bands; the excess is clipped (left unfilled, not carried into a higher band, since steam physically doesn't reach there). Largest clips: chemicals ~14%, pulp/paper/printing ~10%, food/beverage/tobacco ~6% of that category's steam heat. See the 'clip' column on the 'Band Weights' tab for every category.</t>
+  </si>
+  <si>
+    <t>MECS method and the CHP ambiguity</t>
+  </si>
+  <si>
+    <t>MECS reports fuel burned in a CHP/cogeneration unit as a single line, with no split between the electricity/shaft-power output and the useful-heat output. This workbook assumes 60% of CHP fuel is steam output (CHP-steam fraction, 'MECS 2022' tab B1); the published bounds if that assumption were 100% vs. 0% are 48.0% vs. 21.5% manufacturing-wide steam share (national row on the MECS 2022 tab) -- a wide range, and the single biggest source of uncertainty in this workbook. Separately, 35.5% of all manufacturing fuel use nationally is not classified to any end use at all (mostly byproduct/waste fuels MECS never allocates), worst in paper, coke &amp; refined petroleum, and iron &amp; steel (each &gt;40% unclassified) -- treat those category splits, plus wood products, as the least reliable. Every category split also carries an estimated +-5-10% ordinary sampling/footing noise on top of the CHP and unclassified-fuel issues. Full writeup: Industry_ThermalBattery_MECS_SteamShares.md (repo root).</t>
+  </si>
+  <si>
+    <t>Non-MECS Industry Categories and the sensitivity check</t>
+  </si>
+  <si>
+    <t>Industry Categories outside NAICS manufacturing (agriculture and forestry, coal mining, oil and gas extraction, other mining and quarrying, construction) have no MECS steam/direct-heat split available; they default to a 0.10 steam share ('Band Weights' tab B1), i.e. assumed mostly direct-fired. Oil and gas extraction alone is 21.5% of all Industry Categories' total eligible heat in the 2025 band-heat data, so this assumption is doing real work, not a rounding footnote. Sensitivity alternative: 0.399, the manufacturing-wide average steam share at the CHP=0.6 assumption ('MECS 2022' national row) -- i.e., if non-MECS categories instead ran a typical manufacturing steam mix rather than mostly-direct-fired equipment. This alternative is documented here but NOT wired into the shipped calculation; a team decision on which is more defensible for extraction/ag/construction processes (largely field/kiln/dryer direct heat, arguably supporting the 0.10 default) is still open.</t>
   </si>
   <si>
     <t>O&amp;M is separate</t>
   </si>
   <si>
-    <t>Operations &amp; maintenance is NOT included in this capital-cost figure - see TBOM (2% of TBCC per year, an unverified proxy; see TBOM/TBOM.xlsx for that derivation).</t>
-  </si>
-  <si>
-    <t>Derivation chain</t>
-  </si>
-  <si>
-    <t>All formulas are visible on the TBCC tab: component costs (B2:B6) -&gt; system cost per kW-out at low/central/high storage price (B10:B12) -&gt; CPI-U deflation (B15:B17) -&gt; $/(BTU/yr) in 2012 USD (B18:B20). Editing any source cell recomputes the exported value.</t>
+    <t>Operations &amp; maintenance is NOT included in this capital-cost figure -- see TBOM (2% of TBCC per year, an unverified proxy; see TBOM/TBOM.xlsx for that derivation).</t>
+  </si>
+  <si>
+    <t>Band heat basis</t>
+  </si>
+  <si>
+    <t>The 'Band Heat 2025' tab pastes the model's own Thermal Battery Demand Cap in Electricity Equivalent by Industry Category and heat band -- an electricity-equivalent BTU figure, not raw fuel BTU -- because that is the basis the demand cap (and hence eligible adoption) is computed on. It is a single-year (2025) snapshot; the steam-share weights derived from it are not re-derived year by year.</t>
+  </si>
+  <si>
+    <t>KNOWN BOUNDARY AMBIGUITY (component costs, flagged for review)</t>
+  </si>
+  <si>
+    <t>The R&amp;G source report does not state whether component costs are equipment-only or fully installed; the $100/kW-in charging-equipment figure is benchmarked to Li-ion equipment analogs, so an installation/balance-of-plant markup (often 30-100% for industrial equipment) may be missing. NREL Kocher et al. 2024 (Energy &amp; Environmental Science 17:2206, DOI 10.1039/D3EE03594H) could not be retrieved full-text at compilation time and should be checked against this figure before external release. Separately, the R&amp;G $300/kW-out steam-side figure and Stack et al.'s $6.47/kW-out blower figure differ by ~46x with no reconciliation found in either source -- see the blower source entry above.</t>
   </si>
   <si>
     <t>Provenance</t>
   </si>
   <si>
-    <t>Written by Claude Code, issue #387, 2026-08-17; reviewed by: (pending).</t>
+    <t>Component-cost block written by Claude Code, issue #387, 2026-08-17. MECS steam-share derivation (MECS 2022 / Band Heat 2025 / Band Weights / Checks tabs, and this rewritten About tab) written by Claude Code, 2026-08-20, per Industry_ThermalBattery_MECS_SteamShares.md and the session scratchpad script tbcc_weights.py. Reviewed by: (pending).</t>
   </si>
   <si>
     <t>Verification status</t>
   </si>
   <si>
-    <t>All figures herein are inputs for staff review; verify against primary sources before use in any external work product.</t>
+    <t>All figures herein are inputs for staff review, not a finished model input or published position -- verify against the primary sources above before use in any external work product. This document and its assumptions (CHP fraction, non-MECS default, 300C ceiling) are open to revision by the team.</t>
+  </si>
+  <si>
+    <t>18h storage-duration convention (ratified)</t>
+  </si>
+  <si>
+    <t>The 18-hour storage-duration convention used in the 'TBCC Components' tab (24 minus the 6-hour TBCH charging window =&gt; 4.0 kW-in and 18 kWh-th storage per kW-out; see the Sources block above) was ratified by Dan O'Brien, 2026-08-20, as internally consistent with TBCH Thermal Battery Daily Charging Hours (6 h/day) elsewhere in the model. The published literature on optimal thermal-battery storage duration clusters in the 15-24 hour range, and Rissman &amp; Gimon's own reported optimum is 24 hours (i.e., a shorter, ~0-hour charging window) -- a documented alternative, not adopted here, since a 24-hour duration would be inconsistent with the 6-hour TBCH charging-window spec this workbook is built to match. Revisit both together if either changes.</t>
   </si>
   <si>
     <t>Component</t>
@@ -232,13 +303,310 @@
   </si>
   <si>
     <t>TBCC - high</t>
+  </si>
+  <si>
+    <t>Direct-heat discharge equipmt (blower) cost, 2017</t>
+  </si>
+  <si>
+    <t>$/kW-th (2017 USD, installed)</t>
+  </si>
+  <si>
+    <t>Stack, Curtis &amp; Forsberg 2019, Applied Energy, Table 3</t>
+  </si>
+  <si>
+    <t>CPI-U 2017</t>
+  </si>
+  <si>
+    <t>Blower cost inflator, 2017-&gt;2023</t>
+  </si>
+  <si>
+    <t>Direct-heat discharge equipmt cost, 2023 USD</t>
+  </si>
+  <si>
+    <t>$/kW-th (2023 USD, installed)</t>
+  </si>
+  <si>
+    <t>used by Band Weights tab per-band discharge blend</t>
+  </si>
+  <si>
+    <t>CHP-steam fraction (assumption, editable):</t>
+  </si>
+  <si>
+    <t>Share of CHP/cogeneration fuel input attributed to steam output (vs. power/shaft-work output); MECS reports fuel input only, not the heat/power split (see About tab).</t>
+  </si>
+  <si>
+    <t>EPS Industry Category (MECS rollup)</t>
+  </si>
+  <si>
+    <t>Boiler (TBtu)</t>
+  </si>
+  <si>
+    <t>CHP (TBtu)</t>
+  </si>
+  <si>
+    <t>Process Heating (TBtu)</t>
+  </si>
+  <si>
+    <t>Steam share s (this workbook, CHP frac = B1)</t>
+  </si>
+  <si>
+    <t>Steam % incl. all CHP (upper bound)</t>
+  </si>
+  <si>
+    <t>Steam % excl. CHP (lower bound)</t>
+  </si>
+  <si>
+    <t>Not classified to any end use (published, informational)</t>
+  </si>
+  <si>
+    <t>Food, beverage, tobacco</t>
+  </si>
+  <si>
+    <t>Textiles, apparel, leather</t>
+  </si>
+  <si>
+    <t>Wood products</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Coke &amp; refined petroleum</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>Rubber &amp; plastics</t>
+  </si>
+  <si>
+    <t>Glass &amp; cement (non-metallic minerals)</t>
+  </si>
+  <si>
+    <t>Iron &amp; steel</t>
+  </si>
+  <si>
+    <t>Other metals</t>
+  </si>
+  <si>
+    <t>Fabricated metal/machinery/electronics/vehicles</t>
+  </si>
+  <si>
+    <t>Other manufacturing</t>
+  </si>
+  <si>
+    <t>National total (all manufacturing, 311-339)</t>
+  </si>
+  <si>
+    <t>Source: EIA MECS 2022, Table 5.2 "End uses of fuel consumption, 2022" (https://www.eia.gov/consumption/manufacturing/data/2022/xls/Table5_2.xlsx). Rolled up to EPS Industry Categories per Industry_ThermalBattery_MECS_SteamShares.md (repo root), Section 5. National row (E18) is the manufacturing-wide steam share at the CHP assumption in B1 -- used in the About tab as the non-MECS-IC sensitivity alternative (0.399 at CHP frac 0.6).</t>
+  </si>
+  <si>
+    <t>Source: EPS defaults run TB_omrm_newdef, extracted 2026-08-20. Thermal Battery Demand Cap in Electricity Equivalent[Industry Category,Industrial Process], 2025 column, TB_bandheat.tab (BTU/yr, electricity-equivalent).</t>
+  </si>
+  <si>
+    <t>Industry Category</t>
+  </si>
+  <si>
+    <t>heat &lt; 100 C</t>
+  </si>
+  <si>
+    <t>heat 100 - 200 C</t>
+  </si>
+  <si>
+    <t>heat 200 - 500 C</t>
+  </si>
+  <si>
+    <t>heat 500 - 1000 C</t>
+  </si>
+  <si>
+    <t>heat &gt; 1000 C</t>
+  </si>
+  <si>
+    <t>Total heat (all bands)</t>
+  </si>
+  <si>
+    <t>agriculture and forestry 01T03</t>
+  </si>
+  <si>
+    <t>coal mining 05</t>
+  </si>
+  <si>
+    <t>oil and gas extraction 06</t>
+  </si>
+  <si>
+    <t>other mining and quarrying 07T08</t>
+  </si>
+  <si>
+    <t>food beverage and tobacco 10T12</t>
+  </si>
+  <si>
+    <t>textiles apparel and leather 13T15</t>
+  </si>
+  <si>
+    <t>wood products 16</t>
+  </si>
+  <si>
+    <t>pulp paper and printing 17T18</t>
+  </si>
+  <si>
+    <t>refined petroleum and coke 19</t>
+  </si>
+  <si>
+    <t>chemicals 20</t>
+  </si>
+  <si>
+    <t>rubber and plastic products 22</t>
+  </si>
+  <si>
+    <t>glass and glass products 231</t>
+  </si>
+  <si>
+    <t>cement and other nonmetallic minerals 239</t>
+  </si>
+  <si>
+    <t>iron and steel 241</t>
+  </si>
+  <si>
+    <t>other metals 242</t>
+  </si>
+  <si>
+    <t>metal products except machinery and vehicles 25</t>
+  </si>
+  <si>
+    <t>computers and electronics 26</t>
+  </si>
+  <si>
+    <t>appliances and electrical equipment 27</t>
+  </si>
+  <si>
+    <t>other machinery 28</t>
+  </si>
+  <si>
+    <t>road vehicles 29</t>
+  </si>
+  <si>
+    <t>nonroad vehicles 30</t>
+  </si>
+  <si>
+    <t>other manufacturing 31T33</t>
+  </si>
+  <si>
+    <t>energy pipelines and gas processing 352T353</t>
+  </si>
+  <si>
+    <t>water and waste 36T39</t>
+  </si>
+  <si>
+    <t>construction 41T43</t>
+  </si>
+  <si>
+    <t>Non-MECS IC steam share (assumption, editable):</t>
+  </si>
+  <si>
+    <t>Applies to Industry Categories outside NAICS manufacturing (agriculture, mining, oil &amp; gas extraction, construction) and zero-heat categories. Sensitivity alternative 0.399 (manufacturing-wide average at CHP frac 0.6, see 'MECS 2022' national row) is discussed in the About tab, not wired in here.</t>
+  </si>
+  <si>
+    <t>Mapped MECS category (assignment)</t>
+  </si>
+  <si>
+    <t>s_i (steam share)</t>
+  </si>
+  <si>
+    <t>Total heat T_i</t>
+  </si>
+  <si>
+    <t>Steam heat S_i = s_i*T_i</t>
+  </si>
+  <si>
+    <t>cap0 (=heat0)</t>
+  </si>
+  <si>
+    <t>cap1 (=heat1)</t>
+  </si>
+  <si>
+    <t>cap2 (=heat2/3, 300C ceiling)</t>
+  </si>
+  <si>
+    <t>fill0</t>
+  </si>
+  <si>
+    <t>rem1</t>
+  </si>
+  <si>
+    <t>fill1</t>
+  </si>
+  <si>
+    <t>rem2</t>
+  </si>
+  <si>
+    <t>fill2</t>
+  </si>
+  <si>
+    <t>clip (unfilled S_i, &gt;300C)</t>
+  </si>
+  <si>
+    <t>fill3</t>
+  </si>
+  <si>
+    <t>fill4</t>
+  </si>
+  <si>
+    <t>non-MECS default</t>
+  </si>
+  <si>
+    <t>TOTALS</t>
+  </si>
+  <si>
+    <t>Band</t>
+  </si>
+  <si>
+    <t>Band heat total</t>
+  </si>
+  <si>
+    <t>Fill (steam-served) total</t>
+  </si>
+  <si>
+    <t>w_b = fill / heat</t>
+  </si>
+  <si>
+    <t>w_b</t>
+  </si>
+  <si>
+    <t>Discharge cost_b (2023 USD/kW-out)</t>
+  </si>
+  <si>
+    <t>System cost_b (2023 USD/kW-out)</t>
+  </si>
+  <si>
+    <t>TBCC_b (2012 USD/BTU-yr)</t>
+  </si>
+  <si>
+    <t>Verification: computed TBCC_b (Band Weights tab) vs. authoritative TBCC.csv</t>
+  </si>
+  <si>
+    <t>Computed TBCC_b</t>
+  </si>
+  <si>
+    <t>TBCC.csv value</t>
+  </si>
+  <si>
+    <t>Abs % diff</t>
+  </si>
+  <si>
+    <t>Check (&lt;0.5%)</t>
+  </si>
+  <si>
+    <t>Unit: 2012 USD per BTU of annual energy service (electricity equivalent)</t>
+  </si>
+  <si>
+    <t>Capital Cost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,9 +620,19 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -284,18 +662,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,138 +991,258 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="112" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="3">
-        <v>2023</v>
+      <c r="B13" s="2">
+        <v>2019</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="3" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="3" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="2">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="29" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="3" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="33" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B21" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -740,7 +1253,7 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -751,264 +1264,4054 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B2">
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B3">
         <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>1.5</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B5">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <f>24/B7</f>
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B9">
         <f>24-B7</f>
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B10">
         <f>B2*B8+B3+B4*B9</f>
         <v>727</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B11">
         <f>B2*B8+B3+B5*B9</f>
         <v>790</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B12">
         <f>B2*B8+B3+B6*B9</f>
         <v>880</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B13">
         <v>8760</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B14">
         <v>3412.14</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B15">
         <v>229.59399999999999</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="B16">
         <v>304.702</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="B17">
         <f>B15/B16</f>
         <v>0.75350342301658668</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B18">
         <f>B10*B17/(B13*B14)</f>
         <v>1.832688658747222E-5</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="B19">
         <f>B11*B17/(B13*B14)</f>
         <v>1.9915048698903784E-5</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="B20">
         <f>B12*B17/(B13*B14)</f>
         <v>2.2183851715234599E-5</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22">
+        <v>6.47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23">
+        <v>245.12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24">
+        <f>B16/B23</f>
+        <v>1.2430727806788511</v>
+      </c>
+      <c r="C24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25">
+        <f>B22*B24</f>
+        <v>8.0426808909921661</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="8" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="4" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5">
+        <v>168</v>
+      </c>
+      <c r="C5">
+        <v>304</v>
+      </c>
+      <c r="D5">
+        <v>239</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E16" si="0">(B5+$B$1*C5)/(B5+$B$1*C5+D5)</f>
+        <v>0.59450288428910758</v>
+      </c>
+      <c r="F5">
+        <f t="shared" ref="F5:F16" si="1">(B5+C5)/(B5+C5+D5)</f>
+        <v>0.66385372714486635</v>
+      </c>
+      <c r="G5">
+        <f t="shared" ref="G5:G16" si="2">B5/(B5+D5)</f>
+        <v>0.41277641277641275</v>
+      </c>
+      <c r="H5">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>0.42028985507246375</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H6">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0.22018348623853209</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>0.28169014084507044</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="2"/>
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="H7">
+        <v>0.61099999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8">
+        <v>76</v>
+      </c>
+      <c r="C8">
+        <v>378</v>
+      </c>
+      <c r="D8">
+        <v>154</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0.66287215411558664</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>0.74671052631578949</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="2"/>
+        <v>0.33043478260869563</v>
+      </c>
+      <c r="H8">
+        <v>0.58399999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9">
+        <v>112</v>
+      </c>
+      <c r="C9">
+        <v>246</v>
+      </c>
+      <c r="D9">
+        <v>651</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0.28508675598506483</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>0.35480673934588702</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>0.14678899082568808</v>
+      </c>
+      <c r="H9">
+        <v>0.63100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10">
+        <v>484</v>
+      </c>
+      <c r="C10">
+        <v>993</v>
+      </c>
+      <c r="D10">
+        <v>801</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>0.57411739685240326</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>0.6483757682177349</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="2"/>
+        <v>0.37665369649805447</v>
+      </c>
+      <c r="H10">
+        <v>0.217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11">
+        <v>22</v>
+      </c>
+      <c r="C11">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>48</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>0.45080091533180772</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>0.51515151515151514</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="2"/>
+        <v>0.31428571428571428</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+      <c r="D12">
+        <v>582</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>2.0531807472231569E-2</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>2.8380634390651086E-2</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>8.5178875638841564E-3</v>
+      </c>
+      <c r="H12">
+        <v>0.28100000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>35</v>
+      </c>
+      <c r="D13">
+        <v>352</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>8.8082901554404139E-2</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>0.12</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="2"/>
+        <v>3.5616438356164383E-2</v>
+      </c>
+      <c r="H13">
+        <v>0.42899999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>23</v>
+      </c>
+      <c r="D14">
+        <v>189</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>0.103415559772296</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>0.1409090909090909</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="2"/>
+        <v>4.060913705583756E-2</v>
+      </c>
+      <c r="H14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>18</v>
+      </c>
+      <c r="D15">
+        <v>314</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>9.9770642201834847E-2</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>0.11797752808988764</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>7.1005917159763315E-2</v>
+      </c>
+      <c r="H15">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>22</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>0.17910447761194029</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
+      </c>
+      <c r="H16">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18">
+        <v>941</v>
+      </c>
+      <c r="C18">
+        <v>2228</v>
+      </c>
+      <c r="D18">
+        <v>3435</v>
+      </c>
+      <c r="E18">
+        <f>(B18+$B$1*C18)/(B18+$B$1*C18+D18)</f>
+        <v>0.39871866685338192</v>
+      </c>
+      <c r="F18">
+        <f>(B18+C18)/(B18+C18+D18)</f>
+        <v>0.47986069049061175</v>
+      </c>
+      <c r="G18">
+        <f>B18/(B18+D18)</f>
+        <v>0.21503656307129798</v>
+      </c>
+      <c r="H18">
+        <v>0.35499999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3">
+        <v>95182700000000</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G27" si="0">SUM(B3:F3)</f>
+        <v>95182700000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5">
+        <v>67808300000000</v>
+      </c>
+      <c r="C5">
+        <v>266432000000000</v>
+      </c>
+      <c r="D5">
+        <v>1051940000000000</v>
+      </c>
+      <c r="E5">
+        <v>198903000000000</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>1585083300000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6">
+        <v>60351000000000</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>60351000000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7">
+        <v>47231200000000</v>
+      </c>
+      <c r="C7">
+        <v>73812400000000</v>
+      </c>
+      <c r="D7">
+        <v>282194000000000</v>
+      </c>
+      <c r="E7">
+        <v>2383190000</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>403239983190000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8">
+        <v>1237420000000</v>
+      </c>
+      <c r="C8">
+        <v>807725000000</v>
+      </c>
+      <c r="D8">
+        <v>2169290000000</v>
+      </c>
+      <c r="E8">
+        <v>48598600000</v>
+      </c>
+      <c r="F8">
+        <v>70537000000</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>4333570600000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9">
+        <v>8847760000000</v>
+      </c>
+      <c r="C9">
+        <v>45213500000000</v>
+      </c>
+      <c r="D9">
+        <v>114301000000000</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>168362260000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10">
+        <v>142216000000000</v>
+      </c>
+      <c r="C10">
+        <v>190069000000000</v>
+      </c>
+      <c r="D10">
+        <v>558254000000000</v>
+      </c>
+      <c r="E10">
+        <v>32102700000000</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>922641700000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11">
+        <v>314578000000000</v>
+      </c>
+      <c r="C11">
+        <v>329389000000000</v>
+      </c>
+      <c r="D11">
+        <v>889339000000000</v>
+      </c>
+      <c r="E11">
+        <v>206316000000000</v>
+      </c>
+      <c r="F11">
+        <v>55929200000000</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>1795551200000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12">
+        <v>62164400000000</v>
+      </c>
+      <c r="C12">
+        <v>229148000000000</v>
+      </c>
+      <c r="D12">
+        <v>889348000000000</v>
+      </c>
+      <c r="E12">
+        <v>169244000000000</v>
+      </c>
+      <c r="F12">
+        <v>9632490000</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>1349914032490000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13">
+        <v>3131390000000</v>
+      </c>
+      <c r="C13">
+        <v>12579600000000</v>
+      </c>
+      <c r="D13">
+        <v>32111200000000</v>
+      </c>
+      <c r="E13">
+        <v>7323910000000</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>55146100000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>1104560000000</v>
+      </c>
+      <c r="E14">
+        <v>4545930000000</v>
+      </c>
+      <c r="F14">
+        <v>58003100000000</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>63653590000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15">
+        <v>5450870000000</v>
+      </c>
+      <c r="C15">
+        <v>6520840000</v>
+      </c>
+      <c r="D15">
+        <v>14232000000000</v>
+      </c>
+      <c r="E15">
+        <v>56269600000000</v>
+      </c>
+      <c r="F15">
+        <v>153450000000000</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>229408990840000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16">
+        <v>1020910000000</v>
+      </c>
+      <c r="C16">
+        <v>1135030000000</v>
+      </c>
+      <c r="D16">
+        <v>4215560000000</v>
+      </c>
+      <c r="E16">
+        <v>5800080000000</v>
+      </c>
+      <c r="F16">
+        <v>261558000000000</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>273729580000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17">
+        <v>14111700000</v>
+      </c>
+      <c r="C17">
+        <v>23986500000000</v>
+      </c>
+      <c r="D17">
+        <v>63023400000000</v>
+      </c>
+      <c r="E17">
+        <v>13489300000000</v>
+      </c>
+      <c r="F17">
+        <v>33171300000000</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>133684611700000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18">
+        <v>3912250000000</v>
+      </c>
+      <c r="C18">
+        <v>3981140000000</v>
+      </c>
+      <c r="D18">
+        <v>11782400000000</v>
+      </c>
+      <c r="E18">
+        <v>7758640000000</v>
+      </c>
+      <c r="F18">
+        <v>32594200000000</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>60028630000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19">
+        <v>1604630000000</v>
+      </c>
+      <c r="C19">
+        <v>474505000000</v>
+      </c>
+      <c r="D19">
+        <v>1451270000000</v>
+      </c>
+      <c r="E19">
+        <v>1420450000000</v>
+      </c>
+      <c r="F19">
+        <v>1669350000000</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>6620205000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20">
+        <v>2661720000000</v>
+      </c>
+      <c r="C20">
+        <v>863990000000</v>
+      </c>
+      <c r="D20">
+        <v>2842970000000</v>
+      </c>
+      <c r="E20">
+        <v>2379150000000</v>
+      </c>
+      <c r="F20">
+        <v>3110220000000</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>11858050000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21">
+        <v>1887280000000</v>
+      </c>
+      <c r="C21">
+        <v>653526000000</v>
+      </c>
+      <c r="D21">
+        <v>2216080000000</v>
+      </c>
+      <c r="E21">
+        <v>1826220000000</v>
+      </c>
+      <c r="F21">
+        <v>2355420000000</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>8938526000000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22">
+        <v>8324080000000</v>
+      </c>
+      <c r="C22">
+        <v>4706520000000</v>
+      </c>
+      <c r="D22">
+        <v>12801100000000</v>
+      </c>
+      <c r="E22">
+        <v>10838300000</v>
+      </c>
+      <c r="F22">
+        <v>6193520000000</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>32036058300000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23">
+        <v>5065000000000</v>
+      </c>
+      <c r="C23">
+        <v>2494020000000</v>
+      </c>
+      <c r="D23">
+        <v>6449370000000</v>
+      </c>
+      <c r="E23">
+        <v>5883020000</v>
+      </c>
+      <c r="F23">
+        <v>3324550000000</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>17338823020000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24">
+        <v>4690580000000</v>
+      </c>
+      <c r="C24">
+        <v>2190220000000</v>
+      </c>
+      <c r="D24">
+        <v>7423970000000</v>
+      </c>
+      <c r="E24">
+        <v>5882150000000</v>
+      </c>
+      <c r="F24">
+        <v>6096050000000</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>26282970000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27">
+        <v>62863500000000</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>62863500000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:U45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="21" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1">
+        <v>0.1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+    </row>
+    <row r="3" spans="1:21" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4">
+        <f>$B$1</f>
+        <v>0.1</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP($A4,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>95182700000000</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP($A4,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>VLOOKUP($A4,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>VLOOKUP($A4,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>VLOOKUP($A4,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I28" si="0">SUM(D4:H4)</f>
+        <v>95182700000000</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J28" si="1">C4*I4</f>
+        <v>9518270000000</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4:K28" si="2">D4</f>
+        <v>95182700000000</v>
+      </c>
+      <c r="L4">
+        <f t="shared" ref="L4:L28" si="3">E4</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f t="shared" ref="M4:M28" si="4">F4/3</f>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f t="shared" ref="N4:N28" si="5">MIN(K4,J4)</f>
+        <v>9518270000000</v>
+      </c>
+      <c r="O4">
+        <f t="shared" ref="O4:O28" si="6">J4-N4</f>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f t="shared" ref="P4:P28" si="7">MIN(L4,O4)</f>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q28" si="8">O4-P4</f>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R28" si="9">MIN(M4,Q4)</f>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S28" si="10">Q4-R4</f>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5">
+        <f>$B$1</f>
+        <v>0.1</v>
+      </c>
+      <c r="D5">
+        <f>VLOOKUP($A5,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP($A5,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>VLOOKUP($A5,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>VLOOKUP($A5,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>VLOOKUP($A5,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6">
+        <f>$B$1</f>
+        <v>0.1</v>
+      </c>
+      <c r="D6">
+        <f>VLOOKUP($A6,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>67808300000000</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP($A6,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>266432000000000</v>
+      </c>
+      <c r="F6">
+        <f>VLOOKUP($A6,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>1051940000000000</v>
+      </c>
+      <c r="G6">
+        <f>VLOOKUP($A6,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>198903000000000</v>
+      </c>
+      <c r="H6">
+        <f>VLOOKUP($A6,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>1585083300000000</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>158508330000000</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>67808300000000</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>266432000000000</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="4"/>
+        <v>350646666666666.69</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="5"/>
+        <v>67808300000000</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="6"/>
+        <v>90700030000000</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="7"/>
+        <v>90700030000000</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7">
+        <f>$B$1</f>
+        <v>0.1</v>
+      </c>
+      <c r="D7">
+        <f>VLOOKUP($A7,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>60351000000000</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP($A7,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>VLOOKUP($A7,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>VLOOKUP($A7,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>VLOOKUP($A7,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>60351000000000</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>6035100000000</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>60351000000000</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="5"/>
+        <v>6035100000000</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8">
+        <f>VLOOKUP(B8,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.59450288428910758</v>
+      </c>
+      <c r="D8">
+        <f>VLOOKUP($A8,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>47231200000000</v>
+      </c>
+      <c r="E8">
+        <f>VLOOKUP($A8,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>73812400000000</v>
+      </c>
+      <c r="F8">
+        <f>VLOOKUP($A8,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>282194000000000</v>
+      </c>
+      <c r="G8">
+        <f>VLOOKUP($A8,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>2383190000</v>
+      </c>
+      <c r="H8">
+        <f>VLOOKUP($A8,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>403239983190000</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>239727333067146.25</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>47231200000000</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>73812400000000</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="4"/>
+        <v>94064666666666.672</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="5"/>
+        <v>47231200000000</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="6"/>
+        <v>192496133067146.25</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="7"/>
+        <v>73812400000000</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="8"/>
+        <v>118683733067146.25</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="9"/>
+        <v>94064666666666.672</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="10"/>
+        <v>24619066400479.578</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9">
+        <f>VLOOKUP(B9,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.42028985507246375</v>
+      </c>
+      <c r="D9">
+        <f>VLOOKUP($A9,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>1237420000000</v>
+      </c>
+      <c r="E9">
+        <f>VLOOKUP($A9,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>807725000000</v>
+      </c>
+      <c r="F9">
+        <f>VLOOKUP($A9,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>2169290000000</v>
+      </c>
+      <c r="G9">
+        <f>VLOOKUP($A9,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>48598600000</v>
+      </c>
+      <c r="H9">
+        <f>VLOOKUP($A9,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>70537000000</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>4333570600000</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>1821355759420.2898</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>1237420000000</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>807725000000</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="4"/>
+        <v>723096666666.66663</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="5"/>
+        <v>1237420000000</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="6"/>
+        <v>583935759420.28979</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="7"/>
+        <v>583935759420.28979</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10">
+        <f>VLOOKUP(B10,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.22018348623853209</v>
+      </c>
+      <c r="D10">
+        <f>VLOOKUP($A10,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>8847760000000</v>
+      </c>
+      <c r="E10">
+        <f>VLOOKUP($A10,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>45213500000000</v>
+      </c>
+      <c r="F10">
+        <f>VLOOKUP($A10,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>114301000000000</v>
+      </c>
+      <c r="G10">
+        <f>VLOOKUP($A10,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <f>VLOOKUP($A10,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>168362260000000</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>37070589357798.164</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>8847760000000</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>45213500000000</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="4"/>
+        <v>38100333333333.336</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="5"/>
+        <v>8847760000000</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="6"/>
+        <v>28222829357798.164</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="7"/>
+        <v>28222829357798.164</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11">
+        <f>VLOOKUP(B11,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.66287215411558664</v>
+      </c>
+      <c r="D11">
+        <f>VLOOKUP($A11,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>142216000000000</v>
+      </c>
+      <c r="E11">
+        <f>VLOOKUP($A11,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>190069000000000</v>
+      </c>
+      <c r="F11">
+        <f>VLOOKUP($A11,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>558254000000000</v>
+      </c>
+      <c r="G11">
+        <f>VLOOKUP($A11,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>32102700000000</v>
+      </c>
+      <c r="H11">
+        <f>VLOOKUP($A11,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>922641700000000</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>611593491155866.88</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>142216000000000</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>190069000000000</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="4"/>
+        <v>186084666666666.66</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="5"/>
+        <v>142216000000000</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="6"/>
+        <v>469377491155866.88</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="7"/>
+        <v>190069000000000</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="8"/>
+        <v>279308491155866.88</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="9"/>
+        <v>186084666666666.66</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="10"/>
+        <v>93223824489200.219</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12">
+        <f>VLOOKUP(B12,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.28508675598506483</v>
+      </c>
+      <c r="D12">
+        <f>VLOOKUP($A12,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>314578000000000</v>
+      </c>
+      <c r="E12">
+        <f>VLOOKUP($A12,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>329389000000000</v>
+      </c>
+      <c r="F12">
+        <f>VLOOKUP($A12,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>889339000000000</v>
+      </c>
+      <c r="G12">
+        <f>VLOOKUP($A12,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>206316000000000</v>
+      </c>
+      <c r="H12">
+        <f>VLOOKUP($A12,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>55929200000000</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>1795551200000000</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>511887866813090.31</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>314578000000000</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>329389000000000</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="4"/>
+        <v>296446333333333.31</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="5"/>
+        <v>314578000000000</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="6"/>
+        <v>197309866813090.31</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="7"/>
+        <v>197309866813090.31</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13">
+        <f>VLOOKUP(B13,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.57411739685240326</v>
+      </c>
+      <c r="D13">
+        <f>VLOOKUP($A13,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>62164400000000</v>
+      </c>
+      <c r="E13">
+        <f>VLOOKUP($A13,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>229148000000000</v>
+      </c>
+      <c r="F13">
+        <f>VLOOKUP($A13,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>889348000000000</v>
+      </c>
+      <c r="G13">
+        <f>VLOOKUP($A13,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>169244000000000</v>
+      </c>
+      <c r="H13">
+        <f>VLOOKUP($A13,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>9632490000</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>1349914032490000</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>775009130307689.38</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>62164400000000</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>229148000000000</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="4"/>
+        <v>296449333333333.31</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="5"/>
+        <v>62164400000000</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="6"/>
+        <v>712844730307689.38</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="7"/>
+        <v>229148000000000</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="8"/>
+        <v>483696730307689.38</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="9"/>
+        <v>296449333333333.31</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="10"/>
+        <v>187247396974356.06</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14">
+        <f>VLOOKUP(B14,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.45080091533180772</v>
+      </c>
+      <c r="D14">
+        <f>VLOOKUP($A14,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>3131390000000</v>
+      </c>
+      <c r="E14">
+        <f>VLOOKUP($A14,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>12579600000000</v>
+      </c>
+      <c r="F14">
+        <f>VLOOKUP($A14,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>32111200000000</v>
+      </c>
+      <c r="G14">
+        <f>VLOOKUP($A14,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>7323910000000</v>
+      </c>
+      <c r="H14">
+        <f>VLOOKUP($A14,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>55146100000000</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>24859912356979.402</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>3131390000000</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="3"/>
+        <v>12579600000000</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="4"/>
+        <v>10703733333333.334</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="5"/>
+        <v>3131390000000</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="6"/>
+        <v>21728522356979.402</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="7"/>
+        <v>12579600000000</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="8"/>
+        <v>9148922356979.4023</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="9"/>
+        <v>9148922356979.4023</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15">
+        <f>VLOOKUP(B15,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>2.0531807472231569E-2</v>
+      </c>
+      <c r="D15">
+        <f>VLOOKUP($A15,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>VLOOKUP($A15,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>VLOOKUP($A15,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>1104560000000</v>
+      </c>
+      <c r="G15">
+        <f>VLOOKUP($A15,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>4545930000000</v>
+      </c>
+      <c r="H15">
+        <f>VLOOKUP($A15,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>58003100000000</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>63653590000000</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>1306923254796.3647</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="4"/>
+        <v>368186666666.66669</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="6"/>
+        <v>1306923254796.3647</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="8"/>
+        <v>1306923254796.3647</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="9"/>
+        <v>368186666666.66669</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="10"/>
+        <v>938736588129.698</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16">
+        <f>VLOOKUP(B16,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>2.0531807472231569E-2</v>
+      </c>
+      <c r="D16">
+        <f>VLOOKUP($A16,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>5450870000000</v>
+      </c>
+      <c r="E16">
+        <f>VLOOKUP($A16,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>6520840000</v>
+      </c>
+      <c r="F16">
+        <f>VLOOKUP($A16,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>14232000000000</v>
+      </c>
+      <c r="G16">
+        <f>VLOOKUP($A16,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>56269600000000</v>
+      </c>
+      <c r="H16">
+        <f>VLOOKUP($A16,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>153450000000000</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>229408990840000</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>4710181232325.8154</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>5450870000000</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="3"/>
+        <v>6520840000</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="4"/>
+        <v>4744000000000</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="5"/>
+        <v>4710181232325.8154</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17">
+        <f>VLOOKUP(B17,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>8.8082901554404139E-2</v>
+      </c>
+      <c r="D17">
+        <f>VLOOKUP($A17,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>1020910000000</v>
+      </c>
+      <c r="E17">
+        <f>VLOOKUP($A17,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>1135030000000</v>
+      </c>
+      <c r="F17">
+        <f>VLOOKUP($A17,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>4215560000000</v>
+      </c>
+      <c r="G17">
+        <f>VLOOKUP($A17,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>5800080000000</v>
+      </c>
+      <c r="H17">
+        <f>VLOOKUP($A17,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>261558000000000</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>273729580000000</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>24110895647668.391</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>1020910000000</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>1135030000000</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="4"/>
+        <v>1405186666666.6667</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="5"/>
+        <v>1020910000000</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="6"/>
+        <v>23089985647668.391</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="7"/>
+        <v>1135030000000</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="8"/>
+        <v>21954955647668.391</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="9"/>
+        <v>1405186666666.6667</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="10"/>
+        <v>20549768981001.723</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18">
+        <f>VLOOKUP(B18,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.103415559772296</v>
+      </c>
+      <c r="D18">
+        <f>VLOOKUP($A18,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>14111700000</v>
+      </c>
+      <c r="E18">
+        <f>VLOOKUP($A18,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>23986500000000</v>
+      </c>
+      <c r="F18">
+        <f>VLOOKUP($A18,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>63023400000000</v>
+      </c>
+      <c r="G18">
+        <f>VLOOKUP($A18,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>13489300000000</v>
+      </c>
+      <c r="H18">
+        <f>VLOOKUP($A18,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>33171300000000</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>133684611700000</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>13825068951897.531</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>14111700000</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="3"/>
+        <v>23986500000000</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="4"/>
+        <v>21007800000000</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="5"/>
+        <v>14111700000</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="6"/>
+        <v>13810957251897.531</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="7"/>
+        <v>13810957251897.531</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19">
+        <f>VLOOKUP(B19,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>9.9770642201834847E-2</v>
+      </c>
+      <c r="D19">
+        <f>VLOOKUP($A19,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>3912250000000</v>
+      </c>
+      <c r="E19">
+        <f>VLOOKUP($A19,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>3981140000000</v>
+      </c>
+      <c r="F19">
+        <f>VLOOKUP($A19,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>11782400000000</v>
+      </c>
+      <c r="G19">
+        <f>VLOOKUP($A19,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>7758640000000</v>
+      </c>
+      <c r="H19">
+        <f>VLOOKUP($A19,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>32594200000000</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>60028630000000</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>5989094965596.3291</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>3912250000000</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="3"/>
+        <v>3981140000000</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="4"/>
+        <v>3927466666666.6665</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="5"/>
+        <v>3912250000000</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="6"/>
+        <v>2076844965596.3291</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="7"/>
+        <v>2076844965596.3291</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20">
+        <f>VLOOKUP(B20,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>9.9770642201834847E-2</v>
+      </c>
+      <c r="D20">
+        <f>VLOOKUP($A20,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>1604630000000</v>
+      </c>
+      <c r="E20">
+        <f>VLOOKUP($A20,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>474505000000</v>
+      </c>
+      <c r="F20">
+        <f>VLOOKUP($A20,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>1451270000000</v>
+      </c>
+      <c r="G20">
+        <f>VLOOKUP($A20,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>1420450000000</v>
+      </c>
+      <c r="H20">
+        <f>VLOOKUP($A20,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>1669350000000</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>6620205000000</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>660502104357.7981</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>1604630000000</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="3"/>
+        <v>474505000000</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="4"/>
+        <v>483756666666.66669</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="5"/>
+        <v>660502104357.7981</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21">
+        <f>VLOOKUP(B21,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>9.9770642201834847E-2</v>
+      </c>
+      <c r="D21">
+        <f>VLOOKUP($A21,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>2661720000000</v>
+      </c>
+      <c r="E21">
+        <f>VLOOKUP($A21,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>863990000000</v>
+      </c>
+      <c r="F21">
+        <f>VLOOKUP($A21,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>2842970000000</v>
+      </c>
+      <c r="G21">
+        <f>VLOOKUP($A21,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>2379150000000</v>
+      </c>
+      <c r="H21">
+        <f>VLOOKUP($A21,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>3110220000000</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>11858050000000</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>1183085263761.4678</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>2661720000000</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="3"/>
+        <v>863990000000</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="4"/>
+        <v>947656666666.66663</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="5"/>
+        <v>1183085263761.4678</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22">
+        <f>VLOOKUP(B22,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>9.9770642201834847E-2</v>
+      </c>
+      <c r="D22">
+        <f>VLOOKUP($A22,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>1887280000000</v>
+      </c>
+      <c r="E22">
+        <f>VLOOKUP($A22,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>653526000000</v>
+      </c>
+      <c r="F22">
+        <f>VLOOKUP($A22,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>2216080000000</v>
+      </c>
+      <c r="G22">
+        <f>VLOOKUP($A22,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>1826220000000</v>
+      </c>
+      <c r="H22">
+        <f>VLOOKUP($A22,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>2355420000000</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>8938526000000</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>891802479357.79797</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
+        <v>1887280000000</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="3"/>
+        <v>653526000000</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="4"/>
+        <v>738693333333.33337</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="5"/>
+        <v>891802479357.79797</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23">
+        <f>VLOOKUP(B23,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>9.9770642201834847E-2</v>
+      </c>
+      <c r="D23">
+        <f>VLOOKUP($A23,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>8324080000000</v>
+      </c>
+      <c r="E23">
+        <f>VLOOKUP($A23,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>4706520000000</v>
+      </c>
+      <c r="F23">
+        <f>VLOOKUP($A23,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>12801100000000</v>
+      </c>
+      <c r="G23">
+        <f>VLOOKUP($A23,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>10838300000</v>
+      </c>
+      <c r="H23">
+        <f>VLOOKUP($A23,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>6193520000000</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>32036058300000</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>3196258110206.4214</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="2"/>
+        <v>8324080000000</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="3"/>
+        <v>4706520000000</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="4"/>
+        <v>4267033333333.3335</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="5"/>
+        <v>3196258110206.4214</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24">
+        <f>VLOOKUP(B24,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>9.9770642201834847E-2</v>
+      </c>
+      <c r="D24">
+        <f>VLOOKUP($A24,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>5065000000000</v>
+      </c>
+      <c r="E24">
+        <f>VLOOKUP($A24,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>2494020000000</v>
+      </c>
+      <c r="F24">
+        <f>VLOOKUP($A24,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>6449370000000</v>
+      </c>
+      <c r="G24">
+        <f>VLOOKUP($A24,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>5883020000</v>
+      </c>
+      <c r="H24">
+        <f>VLOOKUP($A24,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>3324550000000</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>17338823020000</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>1729905507729.3574</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
+        <v>5065000000000</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="3"/>
+        <v>2494020000000</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="4"/>
+        <v>2149790000000</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="5"/>
+        <v>1729905507729.3574</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25">
+        <f>VLOOKUP(B25,'MECS 2022'!$A$5:$E$16,5,FALSE)</f>
+        <v>0.17910447761194029</v>
+      </c>
+      <c r="D25">
+        <f>VLOOKUP($A25,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>4690580000000</v>
+      </c>
+      <c r="E25">
+        <f>VLOOKUP($A25,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>2190220000000</v>
+      </c>
+      <c r="F25">
+        <f>VLOOKUP($A25,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>7423970000000</v>
+      </c>
+      <c r="G25">
+        <f>VLOOKUP($A25,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>5882150000000</v>
+      </c>
+      <c r="H25">
+        <f>VLOOKUP($A25,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>6096050000000</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>26282970000000</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>4707397611940.2979</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="2"/>
+        <v>4690580000000</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="3"/>
+        <v>2190220000000</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="4"/>
+        <v>2474656666666.6665</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="5"/>
+        <v>4690580000000</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="6"/>
+        <v>16817611940.297852</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="7"/>
+        <v>16817611940.297852</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26">
+        <f>$B$1</f>
+        <v>0.1</v>
+      </c>
+      <c r="D26">
+        <f>VLOOKUP($A26,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f>VLOOKUP($A26,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <f>VLOOKUP($A26,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f>VLOOKUP($A26,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f>VLOOKUP($A26,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C27">
+        <f>$B$1</f>
+        <v>0.1</v>
+      </c>
+      <c r="D27">
+        <f>VLOOKUP($A27,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f>VLOOKUP($A27,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f>VLOOKUP($A27,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f>VLOOKUP($A27,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <f>VLOOKUP($A27,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28">
+        <f>$B$1</f>
+        <v>0.1</v>
+      </c>
+      <c r="D28">
+        <f>VLOOKUP($A28,'Band Heat 2025'!$A$3:$F$27,2,FALSE)</f>
+        <v>62863500000000</v>
+      </c>
+      <c r="E28">
+        <f>VLOOKUP($A28,'Band Heat 2025'!$A$3:$F$27,3,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f>VLOOKUP($A28,'Band Heat 2025'!$A$3:$F$27,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <f>VLOOKUP($A28,'Band Heat 2025'!$A$3:$F$27,5,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <f>VLOOKUP($A28,'Band Heat 2025'!$A$3:$F$27,6,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="0"/>
+        <v>62863500000000</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="1"/>
+        <v>6286350000000</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="2"/>
+        <v>62863500000000</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="5"/>
+        <v>6286350000000</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30">
+        <f>SUM(D4:D28)</f>
+        <v>900243101700000</v>
+      </c>
+      <c r="E30">
+        <f>SUM(E4:E28)</f>
+        <v>1187943196840000</v>
+      </c>
+      <c r="F30">
+        <f>SUM(F4:F28)</f>
+        <v>3947199170000000</v>
+      </c>
+      <c r="G30">
+        <f>SUM(G4:G28)</f>
+        <v>713328833110000</v>
+      </c>
+      <c r="H30">
+        <f>SUM(H4:H28)</f>
+        <v>617535079490000</v>
+      </c>
+      <c r="N30">
+        <f>SUM(N4:N28)</f>
+        <v>691063776397738.63</v>
+      </c>
+      <c r="P30">
+        <f>SUM(P4:P28)</f>
+        <v>839465311759742.88</v>
+      </c>
+      <c r="R30">
+        <f>SUM(R4:R28)</f>
+        <v>587520962356979.25</v>
+      </c>
+      <c r="T30">
+        <f>SUM(T4:T28)</f>
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <f>SUM(U4:U28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33">
+        <f>D30</f>
+        <v>900243101700000</v>
+      </c>
+      <c r="C33">
+        <f>N30</f>
+        <v>691063776397738.63</v>
+      </c>
+      <c r="D33">
+        <f>IFERROR(C33/B33,0)</f>
+        <v>0.76764129055001751</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34">
+        <f>E30</f>
+        <v>1187943196840000</v>
+      </c>
+      <c r="C34">
+        <f>P30</f>
+        <v>839465311759742.88</v>
+      </c>
+      <c r="D34">
+        <f>IFERROR(C34/B34,0)</f>
+        <v>0.70665442084501251</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35">
+        <f>F30</f>
+        <v>3947199170000000</v>
+      </c>
+      <c r="C35">
+        <f>R30</f>
+        <v>587520962356979.25</v>
+      </c>
+      <c r="D35">
+        <f>IFERROR(C35/B35,0)</f>
+        <v>0.14884502581535028</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36">
+        <f>G30</f>
+        <v>713328833110000</v>
+      </c>
+      <c r="C36">
+        <f>T30</f>
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f>IFERROR(C36/B36,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37">
+        <f>H30</f>
+        <v>617535079490000</v>
+      </c>
+      <c r="C37">
+        <f>U30</f>
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <f>IFERROR(C37/B37,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41">
+        <f>D33</f>
+        <v>0.76764129055001751</v>
+      </c>
+      <c r="C41">
+        <f>D33*'TBCC Components'!$B$3+(1-D33)*'TBCC Components'!$B$25</f>
+        <v>232.16117411735425</v>
+      </c>
+      <c r="D41">
+        <f>'TBCC Components'!$B$2*'TBCC Components'!$B$8+C41+'TBCC Components'!$B$5*'TBCC Components'!$B$9</f>
+        <v>722.16117411735422</v>
+      </c>
+      <c r="E41">
+        <f>D41*'TBCC Components'!$B$17/('TBCC Components'!$B$13*'TBCC Components'!$B$14)</f>
+        <v>1.8204905001271704E-5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42">
+        <f>D34</f>
+        <v>0.70665442084501251</v>
+      </c>
+      <c r="C42">
+        <f>D34*'TBCC Components'!$B$3+(1-D34)*'TBCC Components'!$B$25</f>
+        <v>214.3556111374306</v>
+      </c>
+      <c r="D42">
+        <f>'TBCC Components'!$B$2*'TBCC Components'!$B$8+C42+'TBCC Components'!$B$5*'TBCC Components'!$B$9</f>
+        <v>704.35561113743063</v>
+      </c>
+      <c r="E42">
+        <f>D42*'TBCC Components'!$B$17/('TBCC Components'!$B$13*'TBCC Components'!$B$14)</f>
+        <v>1.7756045945757054E-5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43">
+        <f>D35</f>
+        <v>0.14884502581535028</v>
+      </c>
+      <c r="C43">
+        <f>D35*'TBCC Components'!$B$3+(1-D35)*'TBCC Components'!$B$25</f>
+        <v>51.499075590752895</v>
+      </c>
+      <c r="D43">
+        <f>'TBCC Components'!$B$2*'TBCC Components'!$B$8+C43+'TBCC Components'!$B$5*'TBCC Components'!$B$9</f>
+        <v>541.49907559075291</v>
+      </c>
+      <c r="E43">
+        <f>D43*'TBCC Components'!$B$17/('TBCC Components'!$B$13*'TBCC Components'!$B$14)</f>
+        <v>1.3650608178229401E-5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44">
+        <f>D36</f>
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <f>D36*'TBCC Components'!$B$3+(1-D36)*'TBCC Components'!$B$25</f>
+        <v>8.0426808909921661</v>
+      </c>
+      <c r="D44">
+        <f>'TBCC Components'!$B$2*'TBCC Components'!$B$8+C44+'TBCC Components'!$B$5*'TBCC Components'!$B$9</f>
+        <v>498.04268089099219</v>
+      </c>
+      <c r="E44">
+        <f>D44*'TBCC Components'!$B$17/('TBCC Components'!$B$13*'TBCC Components'!$B$14)</f>
+        <v>1.2555119296299631E-5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45">
+        <f>D37</f>
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <f>D37*'TBCC Components'!$B$3+(1-D37)*'TBCC Components'!$B$25</f>
+        <v>8.0426808909921661</v>
+      </c>
+      <c r="D45">
+        <f>'TBCC Components'!$B$2*'TBCC Components'!$B$8+C45+'TBCC Components'!$B$5*'TBCC Components'!$B$9</f>
+        <v>498.04268089099219</v>
+      </c>
+      <c r="E45">
+        <f>D45*'TBCC Components'!$B$17/('TBCC Components'!$B$13*'TBCC Components'!$B$14)</f>
+        <v>1.2555119296299631E-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4">
+        <f>'Band Weights'!E41</f>
+        <v>1.8204905001271704E-5</v>
+      </c>
+      <c r="C4">
+        <v>1.8206000000000002E-5</v>
+      </c>
+      <c r="D4">
+        <f>ABS(B4-C4)/C4</f>
+        <v>6.0144937289755479E-5</v>
+      </c>
+      <c r="E4" t="str">
+        <f>IF(D4&lt;0.005,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5">
+        <f>'Band Weights'!E42</f>
+        <v>1.7756045945757054E-5</v>
+      </c>
+      <c r="C5">
+        <v>1.7757E-5</v>
+      </c>
+      <c r="D5">
+        <f>ABS(B5-C5)/C5</f>
+        <v>5.3728346170301854E-5</v>
+      </c>
+      <c r="E5" t="str">
+        <f>IF(D5&lt;0.005,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6">
+        <f>'Band Weights'!E43</f>
+        <v>1.3650608178229401E-5</v>
+      </c>
+      <c r="C6">
+        <v>1.3651E-5</v>
+      </c>
+      <c r="D6">
+        <f>ABS(B6-C6)/C6</f>
+        <v>2.870278885057038E-5</v>
+      </c>
+      <c r="E6" t="str">
+        <f>IF(D6&lt;0.005,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7">
+        <f>'Band Weights'!E44</f>
+        <v>1.2555119296299631E-5</v>
+      </c>
+      <c r="C7">
+        <v>1.2554999999999999E-5</v>
+      </c>
+      <c r="D7">
+        <f>ABS(B7-C7)/C7</f>
+        <v>9.5018956297799697E-6</v>
+      </c>
+      <c r="E7" t="str">
+        <f>IF(D7&lt;0.005,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8">
+        <f>'Band Weights'!E45</f>
+        <v>1.2555119296299631E-5</v>
+      </c>
+      <c r="C8">
+        <v>1.2554999999999999E-5</v>
+      </c>
+      <c r="D8">
+        <f>ABS(B8-C8)/C8</f>
+        <v>9.5018956297799697E-6</v>
+      </c>
+      <c r="E8" t="str">
+        <f>IF(D8&lt;0.005,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF1F3864"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2">
+        <f>'Band Weights'!E41</f>
+        <v>1.8204905001271704E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3">
+        <f>'Band Weights'!E42</f>
+        <v>1.7756045945757054E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4">
+        <f>'Band Weights'!E43</f>
+        <v>1.3650608178229401E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5">
+        <f>'Band Weights'!E44</f>
+        <v>1.2555119296299631E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6">
+        <f>'Band Weights'!E45</f>
+        <v>1.2555119296299631E-5</v>
       </c>
     </row>
   </sheetData>
